--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260429_205029.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260429_205029.xlsx
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260429_205029.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260429_205029.xlsx
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
